--- a/Pathfinder_Cost_Summary_EN.xlsx
+++ b/Pathfinder_Cost_Summary_EN.xlsx
@@ -8279,7 +8279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -8453,49 +8453,49 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12">
-        <f> FINAL COST (with TP)</f>
-        <v/>
-      </c>
-      <c r="B16" s="13">
-        <f>SUM(B10:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="14">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Supermetal - GDT Integration/Assembly (railcar modification, direct cost)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>707790.6</v>
+      </c>
+      <c r="C16" s="3">
         <f>B16/$B$3</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>FINAL COST (with TP):</t>
+        </is>
+      </c>
+      <c r="B17" s="13">
+        <f>SUM(B10:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="14">
+        <f>B17/$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>2) MARGIN (TDM applied on cost WITHOUT TP; TP is added back afterwards with no markup)</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Base for margin (Final Cost - TP)</t>
-        </is>
-      </c>
-      <c r="B19" s="4">
-        <f>B16-B12</f>
-        <v/>
-      </c>
-      <c r="C19" s="3">
-        <f>B19/$B$3</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Net Price w/o TP (Base / (1 - TDM))</t>
+          <t>Base for margin (Final Cost - TP)</t>
         </is>
       </c>
       <c r="B20" s="4">
-        <f>B19/(1-$B$4)</f>
+        <f>B17-B12</f>
         <v/>
       </c>
       <c r="C20" s="3">
@@ -8504,49 +8504,50 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12">
-        <f> NET PRICE ('OUR PRICE' - cost + margin, before pass-through taxes)</f>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Net Price w/o TP (Base / (1 - TDM))</t>
+        </is>
+      </c>
+      <c r="B21" s="4">
+        <f>B20/(1-$B$4)</f>
         <v/>
       </c>
-      <c r="B21" s="13">
-        <f>B20+B12</f>
-        <v/>
-      </c>
-      <c r="C21" s="14">
+      <c r="C21" s="3">
         <f>B21/$B$3</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>NET PRICE ('OUR PRICE' - cost + margin, before pass-through taxes):</t>
+        </is>
+      </c>
+      <c r="B22" s="13">
+        <f>B21+B12</f>
+        <v/>
+      </c>
+      <c r="C22" s="14">
+        <f>B22/$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>3) PASS-THROUGH TAXES (do not affect our margin - the client pays, client can credit part of it)</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>+ PIS/COFINS (gross-up, tax-inclusive)</t>
-        </is>
-      </c>
-      <c r="B24" s="4">
-        <f>B21/(1-$B$5)</f>
-        <v/>
-      </c>
-      <c r="C24" s="3">
-        <f>B24/$B$3</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>+ ICMS (gross-up, tax-inclusive, stacked on top of PIS/COFINS)</t>
+          <t>+ PIS/COFINS (gross-up, tax-inclusive)</t>
         </is>
       </c>
       <c r="B25" s="4">
-        <f>B24/(1-$B$6)</f>
+        <f>B22/(1-$B$5)</f>
         <v/>
       </c>
       <c r="C25" s="3">
@@ -8557,11 +8558,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>+ IPI (added on top, % of the value already including ICMS)</t>
+          <t>+ ICMS (gross-up, tax-inclusive, stacked on top of PIS/COFINS)</t>
         </is>
       </c>
       <c r="B26" s="4">
-        <f>B25*$B$7</f>
+        <f>B25/(1-$B$6)</f>
         <v/>
       </c>
       <c r="C26" s="3">
@@ -8570,84 +8571,108 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12">
-        <f> FINAL CLIENT PRICE (all taxes included)</f>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>+ IPI (added on top, % of the value already including ICMS)</t>
+        </is>
+      </c>
+      <c r="B27" s="4">
+        <f>B26*$B$7</f>
         <v/>
       </c>
-      <c r="B27" s="13">
-        <f>B25+B26</f>
-        <v/>
-      </c>
-      <c r="C27" s="14">
+      <c r="C27" s="3">
         <f>B27/$B$3</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>FINAL CLIENT PRICE (all taxes included):</t>
+        </is>
+      </c>
+      <c r="B28" s="13">
+        <f>B26+B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="14">
+        <f>B28/$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Notes / Assumptions:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>- Methodology: 'Material Pricing' + 'Approval Summary' tabs of Material Pricing.xlsm (P&amp;L Old was discarded - its formulas are broken / #REF!).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>- TP is treated as WBT USA's own margin (GM WBT USA); it feeds the cost base but is excluded from WBT Brazil's own margin base (TDM = (TP + GM BRZ) / Net Price).</t>
+          <t>- Methodology: 'Material Pricing' + 'Approval Summary' tabs of Material Pricing.xlsm (P&amp;L Old was discarded - its formulas are broken / #REF!).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>- International and Domestic Freight: real values from the China Gate import cost quote (Planilha de Custos de Importacao - Pathfinder - Set 26.xlsx), not the old 9%/3% assumptions.</t>
+          <t>- TP is treated as WBT USA's own margin (GM WBT USA); it feeds the cost base but is excluded from WBT Brazil's own margin base (TDM = (TP + GM BRZ) / Net Price).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>- II/IPI/PIS-COFINS: real per-NCM rate (Material Pricing's 'II' tab) for the 6 priced imported items with a confirmed NCM; worst-case flat rate (our old blended assumption) for the other 41 without one.</t>
+          <t>- International and Domestic Freight: real values from the China Gate import cost quote (Planilha de Custos de Importacao - Pathfinder - Set 26.xlsx), not the old 9%/3% assumptions.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>- ICMS: flat 18% (same value used in Material Pricing's own real example).</t>
+          <t>- II/IPI/PIS-COFINS: real per-NCM rate (Material Pricing's 'II' tab) for the 6 priced imported items with a confirmed NCM; worst-case flat rate (our old blended assumption) for the other 41 without one.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>- 88 PAC items are summed as a single block (already an all-in local cost, not decomposed into TP/freight/duty).</t>
+          <t>- ICMS: flat 18% (same value used in Material Pricing's own real example).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>- 27 items still without a cost quote (Missing) are NOT included in this total - see the Item List tab (Cost Source = MISSING).</t>
+          <t>- 88 PAC items are summed as a single block (already an all-in local cost, not decomposed into TP/freight/duty).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
+          <t>- Supermetal's GDT Integration/Assembly cost (railcar refurbishment: lid, door, ladder, harnesses, battery skid, Fastbrake piping, AC, ballast) is included as a direct cost, feeding the same margin base as the equipment - see the 'GDT Integration and Assembly' tab in the main working file for the line-item breakdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>- 27 items still without a cost quote (Missing) are NOT included in this total - see the Item List tab (Cost Source = MISSING).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
           <t>- QQP (service taxes) and ISS (tax on the GDT integration/labor rollup) were disregarded for now, as requested.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A36:F36"/>
@@ -8656,7 +8681,7 @@
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pathfinder_Cost_Summary_EN.xlsx
+++ b/Pathfinder_Cost_Summary_EN.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item List" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary (P&amp;L)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price Calc Detail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item List'!$A$3:$M$165</definedName>
@@ -57,7 +58,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +75,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,6 +128,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -624,7 +640,6 @@
           <t>90328990</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -667,7 +682,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -710,7 +724,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -753,7 +766,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -796,7 +808,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -839,7 +850,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -882,7 +892,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -925,7 +934,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -968,7 +976,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1016,7 +1023,6 @@
           <t>85371090</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1059,7 +1065,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1102,7 +1107,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1145,7 +1149,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1188,7 +1191,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1231,7 +1233,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1284,7 +1285,6 @@
           <t>24x10x20</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1337,7 +1337,6 @@
           <t>20x3.5x25.5</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1380,7 +1379,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -1418,7 +1416,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -1456,7 +1453,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1509,7 +1505,6 @@
           <t>18.5x8.5x15</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1562,7 +1557,6 @@
           <t>18.5x8.5x15</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1615,7 +1609,6 @@
           <t>14.25x14.25x10</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1668,7 +1661,6 @@
           <t>17.2x1.95x11.2</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1711,7 +1703,6 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1762,7 +1753,6 @@
           <t>14x6x8.5</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1855,7 +1845,6 @@
         <v>761</v>
       </c>
       <c r="H31" s="4" t="n"/>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1906,7 +1895,6 @@
           <t>20.5x10.5x11.5</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1954,7 +1942,6 @@
           <t>85381000</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2007,7 +1994,6 @@
           <t>3.5x0.75x0.75</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2042,7 +2028,6 @@
         <v>411.22</v>
       </c>
       <c r="H35" s="4" t="n"/>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2077,7 +2062,6 @@
         <v>404.6239</v>
       </c>
       <c r="H36" s="4" t="n"/>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2130,7 +2114,6 @@
           <t>7x4x7</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2184,7 +2167,6 @@
           <t>11.8x6.4x8.05</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2237,7 +2219,6 @@
           <t>12.8x3.8x9.5</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2290,7 +2271,6 @@
           <t>8.4x3.35x7.5</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2343,7 +2323,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2396,7 +2375,6 @@
           <t>13.5x5.25x7</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2431,7 +2409,6 @@
         <v>205</v>
       </c>
       <c r="H43" s="4" t="n"/>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2484,7 +2461,6 @@
           <t>24x20x24</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2519,7 +2495,6 @@
         <v>171.544</v>
       </c>
       <c r="H45" s="4" t="n"/>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2554,7 +2529,6 @@
         <v>159</v>
       </c>
       <c r="H46" s="4" t="n"/>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2607,7 +2581,6 @@
           <t>3x2x3</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2660,7 +2633,6 @@
           <t>6x2.25x3</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2713,7 +2685,6 @@
           <t>9.35x5.3x5.2</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2766,7 +2737,6 @@
           <t>3.875x1.625x2.125</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2819,7 +2789,6 @@
           <t>3x0.75x1.5</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2872,7 +2841,6 @@
           <t>7x3.25x4.75</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2925,7 +2893,6 @@
           <t>5.2x2.9x3.35</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2978,7 +2945,6 @@
           <t>4.52x1.35x6.95</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3031,7 +2997,6 @@
           <t>12x0.5x0.5</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3084,7 +3049,6 @@
           <t>4x2.5x2.5</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3139,7 +3103,6 @@
           <t>2.9x0.5x0.5</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3187,7 +3150,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3240,7 +3202,6 @@
           <t>1.75x3.25x2.75</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3293,7 +3254,6 @@
           <t>9.5x1.5x9.5</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3347,7 +3307,6 @@
           <t>2x1x1</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3400,7 +3359,6 @@
           <t>1x0.125x0.125</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3453,7 +3411,6 @@
           <t>12x3x7.5</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3488,7 +3445,6 @@
         <v>79.83</v>
       </c>
       <c r="H64" s="4" t="n"/>
-      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3541,7 +3497,6 @@
           <t>2.5x1.5x1.5</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3589,7 +3544,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3624,7 +3578,6 @@
         <v>72.41</v>
       </c>
       <c r="H67" s="4" t="n"/>
-      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3659,7 +3612,6 @@
         <v>71.94</v>
       </c>
       <c r="H68" s="4" t="n"/>
-      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3694,7 +3646,6 @@
         <v>71.94</v>
       </c>
       <c r="H69" s="4" t="n"/>
-      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3742,7 +3693,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3795,7 +3745,6 @@
           <t>4x2.125x2.125</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3848,7 +3797,6 @@
           <t>1.95x2.7x1.8</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3901,7 +3849,6 @@
           <t>4.75x1.25x4</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3949,7 +3896,6 @@
           <t>1.5x1x1.5</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3984,7 +3930,6 @@
         <v>59.75</v>
       </c>
       <c r="H75" s="4" t="n"/>
-      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4032,7 +3977,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4080,7 +4024,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4134,7 +4077,6 @@
           <t>4x2x4</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4182,7 +4124,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4235,7 +4176,6 @@
           <t>5.85x1.95x3.9</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4283,7 +4223,6 @@
           <t>3.95x1.25x6.65</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4337,7 +4276,6 @@
           <t>4x2x3</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4390,7 +4328,6 @@
           <t>3.1x0.7x2.45</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4443,7 +4380,6 @@
           <t>3x2x2.55</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4497,7 +4433,6 @@
           <t>2.9x2.45x3.05</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4545,7 +4480,6 @@
           <t>85359090</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4598,7 +4532,6 @@
           <t>9x1.5x9</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4652,7 +4585,6 @@
           <t>4x1x4</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4700,7 +4632,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4736,7 +4667,6 @@
         <v>45.7356</v>
       </c>
       <c r="H90" s="4" t="n"/>
-      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4789,7 +4719,6 @@
           <t>4.5x5.25x4.5</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4842,7 +4771,6 @@
           <t>5.8x3.5x4.5</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4895,7 +4823,6 @@
           <t>3x1x2</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4948,7 +4875,6 @@
           <t>0.75x0.1x0.1</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5002,7 +4928,6 @@
           <t>2.5x1.25x1.25</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5056,7 +4981,6 @@
           <t>3.5x2x3.25</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5109,7 +5033,6 @@
           <t>17x1.25x12.625</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5162,7 +5085,6 @@
           <t>2.5x0.65x3.05</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5215,7 +5137,6 @@
           <t>1x0.001x0.001</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5269,7 +5190,6 @@
           <t>3.1x1.45x2.5</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5323,7 +5243,6 @@
           <t>2.5x1.5x3.25</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5376,7 +5295,6 @@
           <t>2.5x1.5x2.5</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5429,7 +5347,6 @@
           <t>2.5x1.5x3</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5482,7 +5399,6 @@
           <t>2.5x1.5x3.25</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5535,7 +5451,6 @@
           <t>3.1x1.45x2.5</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5588,7 +5503,6 @@
           <t>3x1.5x2.5</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5641,7 +5555,6 @@
           <t>6.375x6.375x1.5</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5694,7 +5607,6 @@
           <t>3.05x2.2x4.7</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5747,7 +5659,6 @@
           <t>12.75x3.375x2.75</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5800,7 +5711,6 @@
           <t>8.125x1.625x2</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5835,7 +5745,6 @@
         <v>13.66</v>
       </c>
       <c r="H111" s="4" t="n"/>
-      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5888,7 +5797,6 @@
           <t>1.7x0.95x1.75</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5941,7 +5849,6 @@
           <t>2x1x2</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5994,7 +5901,6 @@
           <t>0.125x0.125x0.25</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6048,7 +5954,6 @@
           <t>4.5x1.48x1.48</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6101,7 +6006,6 @@
           <t>3.05x0.7x2.45</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6154,7 +6058,6 @@
           <t>2.5x1x1</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6207,7 +6110,6 @@
           <t>1x0.001x0.001</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6260,7 +6162,6 @@
           <t>3.75x4.15x7.5</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6313,7 +6214,6 @@
           <t>1.75x0.375x1.75</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6366,7 +6266,6 @@
           <t>1.55x1x1</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6419,7 +6318,6 @@
           <t>1.25x0.75x0.75</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6472,7 +6370,6 @@
           <t>2x1x1</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6525,7 +6422,6 @@
           <t>5.1x1.15x2.95</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6581,7 +6477,6 @@
           <t>1x0.1x0.1</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6634,7 +6529,6 @@
           <t>1.125x0.25x0.25</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6687,7 +6581,6 @@
           <t>5.1x1.15x2.95</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6740,7 +6633,6 @@
           <t>1.65x1.05x1.65</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6794,7 +6686,6 @@
           <t>1.6x1.05x1.7</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6848,7 +6739,6 @@
           <t>1.25x1.05x1.3</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6901,7 +6791,6 @@
           <t>7.1x2.9x6.45</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6954,7 +6843,6 @@
           <t>4x0.5x1</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7007,7 +6895,6 @@
           <t>0.25x0.005x0.25</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7060,7 +6947,6 @@
           <t>0.4x0.3x1</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7113,7 +6999,6 @@
           <t>1.95x0.55x1</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7166,7 +7051,6 @@
           <t>0.85x0.3x1</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7219,7 +7103,6 @@
           <t>0.05x0.05x0.1</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7272,7 +7155,6 @@
           <t>0.05x0.05x0.05</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7307,7 +7189,6 @@
         <v>0.01</v>
       </c>
       <c r="H139" s="4" t="n"/>
-      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7342,7 +7223,6 @@
         <v>0.01</v>
       </c>
       <c r="H140" s="4" t="n"/>
-      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8685,4 +8565,948 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PRICE CALCULATION DETAIL - source and formula for every number</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Use this tab to answer 'why is this number X' - every line cites its source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>0) REALITY CHECK vs. US domestic price</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>US Domestic Reference Price (input - type the real one here):</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Our Price (Net - cost + margin, before Brazilian pass-through taxes):</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>945272.4347593583</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>&lt;- this is the number that is actually comparable to a US domestic sale (no BR import/consumption tax).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Final Client Price (with all Brazilian taxes):</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>1405909.269713061</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gap vs. US reference (Net Price):</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>B6-B5</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
+        <f>B8/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gap vs. US reference (Final Client Price):</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>B7-B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="17">
+        <f>B9/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>KEY POINT: our Net Price is close to the US reference price - the big jump to the Final Client Price comes entirely from Brazilian</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>import duty (II) and consumption taxes (IPI/PIS/COFINS/ICMS), which do not exist in a US domestic sale and would apply just the</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>same whether we import components or a finished, ready-built railcar (a finished vehicle may in fact face a higher/different II bracket -</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>worth confirming with an auto/rail import specialist before assuming 'buy it finished' avoids this tax cascade).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>1) FULL WATERFALL (matches the 'Executive Summary (P&amp;L)' tab, expanded with sources)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Formula / Logic</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Cumulative Multiplier</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Source / Justification</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Raw Cost - Imported Items</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>BOM USD unit x Qty x FX rate, summed over 47 priced imported items</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1346980.92</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>264113.905882353</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.00x</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Final Cost List tab, column F (BOM Price USD Unit) x column E (Quantity), FX from Material Pricing.xlsm 'RATES' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Raw Cost - PAC Items</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Sum of PAC unit cost (BRL) x Qty over 88 PAC-sourced items</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>166060.16</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>32560.81568627451</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9.11x</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>7-PAC Item Costs.xlsx 'aco_cost' field per item, already a fully-loaded local manufacturing cost (materials+labor+overhead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TP - Transfer Price</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>13% on items that already carried some TP historically; 17.2% on items that had none</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>198163.69</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>38855.62549019608</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8.64x</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Matheus's directive this session; 17.2%/0% split originally sourced from the color-coded review copy (yellow/green)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>International Freight</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>1.2295642% of (Raw Cost + TP)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>18998.55</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3725.205882352941</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>91.07x</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>'Planilha de Custos de Importacao - Pathfinder - Set 26.xlsx' (China Gate customs broker quote), Frete+Seguro / Product Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>II - Import Duty</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Blended 17.96% on (Raw Cost+TP+Freight): real per-NCM rate for the 6 items with a confirmed NCM, worst-case 18% flat for the other 41</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>280915.82</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>55081.53333333334</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7.16x</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Material Pricing.xlsm 'II' tab (real NCM lookup) + our prior flat assumption as fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Domestic Freight</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Real flat quote for the whole shipment (Santos -&gt; Betim/Contagem, MG)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>21753.1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>4265.313725490196</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>93.45x</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>China Gate quote 'Despesas de Importacao' tab: Siscomex, despachante, armazenagem, road transport, Marinha Mercante, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Supermetal - GDT Integration/Assembly</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Direct cost: railcar refurbishment (lid, door, ladder, harnesses, battery skid, Fastbrake piping, AC, ballast)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>707790.6</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>138782.4705882353</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.87x</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>'GDT Integration and Assembly' tab, sum of Direct Cost BRL column (18 line items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>FINAL COST (with TP):</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>2740662.84</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>537384.8705882353</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>2) MARGIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Base for margin</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Final Cost - TP (TP is excluded from our own margin base - it's WBT USA's margin, not ours)</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Approval Summary tab of Material Pricing.xlsm: TDM = (TP + GM_BRZ) / Net Price. Algebraically this is equivalent to computing margin on (cost - TP) and adding TP back after, which is what this line does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Target margin (TDM)</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Editable - see the Executive Summary (P&amp;L) tab cell B4</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Matheus's target for this exercise: 45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>NET PRICE ('OUR PRICE'):</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>4820889.417272727</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>945272.4347593583</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.759x</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>3) PASS-THROUGH TAXES (client pays; do not affect our margin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PIS/COFINS</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Net Price / (1 - 10.06%) - gross-up, blended real-NCM rate</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Material Pricing.xlsm 'II' tab (real per-NCM PIS+COFINS) for known items, worst-case 9.25% for the rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ICMS</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Previous subtotal / (1 - 18%) - gross-up, stacked on top of PIS/COFINS</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Flat 18%, matches Material Pricing's own worked example. NOT yet validated against the client's specific destination-state ICMS rate (Tabela ICMS / Aliquotas Basicas tabs have the real origin-destination matrix if needed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IPI</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Previous subtotal x blended IPI% - added on top, not a gross-up</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Material Pricing.xlsm 'II' tab (real per-NCM IPI) for known items, worst-case 9.75% for the rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>FINAL CLIENT PRICE:</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>7170137.27553661</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>1405909.269713061</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2.616x</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>4) ASSUMPTIONS REGISTER (challenge a specific input here, not the whole number)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Value Used</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Where it could be wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Exchange Rate</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5.10 BRL/USD</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>Fixed snapshot from Material Pricing.xlsm; will drift with the real FX on invoice date</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TP rate split</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>13% / 17.2%</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>Arbitrary split chosen this session, not from an official WBT transfer pricing policy document</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>International Freight</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1.23% of value</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>Real broker quote, but only a simulation per the quote's own disclaimer - confirm with actual booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Domestic Freight</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>R$21,753.10 flat</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>Real broker quote for Santos-&gt;Betim/Contagem specifically; changes if origin/destination changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>II (Import Duty)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>17.96% blended (6 of 47 imported items on real NCM)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>41 of 47 imported items still use the worst-case 18% default - no NCM confirmed for them yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PIS/COFINS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10.06% blended</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>Same NCM-coverage gap as II</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>IPI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>9.69% blended</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Same NCM-coverage gap as II</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ICMS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>18% flat</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>Not looked up per origin-destination UF pair; real rate could be lower (interstate) or have RBC reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Deal Margin (TDM)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>N/A - business decision</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>This is the single biggest lever on the final price - see the sensitivity table below</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PAC items</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Treated as one all-in lump, no TP/freight/duty decomposition</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>PAC cost is a genuine local Brazilian manufacturing cost buildup, not an import transaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Missing items</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>27 items excluded (no cost yet)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>Final price will increase once these get quotes - see 'Missing Items' tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Supermetal / GDT rollup</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Treated as local cost, no import duty applied (correct, it's Brazilian labor+materials)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>Does not yet include ISS (service tax) on the labor portion - disregarded for now per Matheus's instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>5) MARGIN SENSITIVITY (same cost base, different TDM targets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>TDM</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>Net Price (Our Price) USD</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>Final Client Price USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>751040.2613445378</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1117026.612143629</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>805823.6948717949</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1198506.336073469</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>869737.7006535948</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1293566.013991615</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="B60" s="21" t="n">
+        <v>945272.4347593583</v>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>1405909.269713061</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1035914.115686275</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1540721.176578796</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1146698.392374728</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1705491.28497025</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Notes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>- This tab is a companion to 'Executive Summary (P&amp;L)' - same numbers, but every line explains itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>- QQP (service taxes) and ISS on the Supermetal/labor portion were disregarded for now, as requested - the final price could increase once those are added.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D49:F49"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Pathfinder_Cost_Summary_EN.xlsx
+++ b/Pathfinder_Cost_Summary_EN.xlsx
@@ -8728,7 +8728,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Cumulative Multiplier</t>
+          <t>Multiplier vs. Final Cost (subtotals only)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.00x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9.11x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8.64x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>91.07x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7.16x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>93.45x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
@@ -8944,6 +8944,11 @@
       </c>
       <c r="D24" s="14" t="n">
         <v>537384.8705882353</v>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>1.000x (baseline)</t>
+        </is>
       </c>
     </row>
     <row r="26">

--- a/Pathfinder_Cost_Summary_EN.xlsx
+++ b/Pathfinder_Cost_Summary_EN.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item List" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary (P&amp;L)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price Calc Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item List'!$A$3:$M$165</definedName>
@@ -20,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="\R\$\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -110,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -137,6 +139,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9514,4 +9526,1122 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SIMULATION - what really makes the Pathfinder Iron Ore Car expensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Change the two yellow switches; the comparison table on the right never depends on them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>SWITCHES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Remove import duty (II) from everything?  (1 = yes, 0 = no)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Battery sets  (2 = current BOM, 1 = a single set)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>BASE VALUES (read from the P&amp;L tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Exchange rate</t>
+        </is>
+      </c>
+      <c r="B9" s="22">
+        <f>'Executive Summary (P&amp;L)'!B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Total Deal Margin (TDM)</t>
+        </is>
+      </c>
+      <c r="B10" s="17">
+        <f>'Executive Summary (P&amp;L)'!B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PIS/COFINS</t>
+        </is>
+      </c>
+      <c r="B11" s="17">
+        <f>'Executive Summary (P&amp;L)'!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ICMS</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
+        <f>'Executive Summary (P&amp;L)'!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IPI</t>
+        </is>
+      </c>
+      <c r="B13" s="17">
+        <f>'Executive Summary (P&amp;L)'!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>US domestic reference price (USD, input)</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Selected (switches) - BRL</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Selected (switches) - USD</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Base (current) - BRL</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Base (current) - USD</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>No import duty (II) - BRL</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>No import duty (II) - USD</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1 battery set - BRL</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1 battery set - USD</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>No II + 1 battery set - BRL</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>No II + 1 battery set - USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Raw cost - imported items</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>$B$48+$C$48*($B$6)</f>
+        <v/>
+      </c>
+      <c r="C19" s="25">
+        <f>B19/$B$9</f>
+        <v/>
+      </c>
+      <c r="D19" s="4">
+        <f>$B$48+$C$48*(2)</f>
+        <v/>
+      </c>
+      <c r="E19" s="3">
+        <f>D19/$B$9</f>
+        <v/>
+      </c>
+      <c r="F19" s="4">
+        <f>$B$48+$C$48*(2)</f>
+        <v/>
+      </c>
+      <c r="G19" s="3">
+        <f>F19/$B$9</f>
+        <v/>
+      </c>
+      <c r="H19" s="4">
+        <f>$B$48+$C$48*(1)</f>
+        <v/>
+      </c>
+      <c r="I19" s="3">
+        <f>H19/$B$9</f>
+        <v/>
+      </c>
+      <c r="J19" s="4">
+        <f>$B$48+$C$48*(1)</f>
+        <v/>
+      </c>
+      <c r="K19" s="3">
+        <f>J19/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Raw cost - PAC items</t>
+        </is>
+      </c>
+      <c r="B20" s="24">
+        <f>$B$49</f>
+        <v/>
+      </c>
+      <c r="C20" s="25">
+        <f>B20/$B$9</f>
+        <v/>
+      </c>
+      <c r="D20" s="4">
+        <f>$B$49</f>
+        <v/>
+      </c>
+      <c r="E20" s="3">
+        <f>D20/$B$9</f>
+        <v/>
+      </c>
+      <c r="F20" s="4">
+        <f>$B$49</f>
+        <v/>
+      </c>
+      <c r="G20" s="3">
+        <f>F20/$B$9</f>
+        <v/>
+      </c>
+      <c r="H20" s="4">
+        <f>$B$49</f>
+        <v/>
+      </c>
+      <c r="I20" s="3">
+        <f>H20/$B$9</f>
+        <v/>
+      </c>
+      <c r="J20" s="4">
+        <f>$B$49</f>
+        <v/>
+      </c>
+      <c r="K20" s="3">
+        <f>J20/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TP - Transfer Price</t>
+        </is>
+      </c>
+      <c r="B21" s="24">
+        <f>$B$50+$C$50*($B$6)</f>
+        <v/>
+      </c>
+      <c r="C21" s="25">
+        <f>B21/$B$9</f>
+        <v/>
+      </c>
+      <c r="D21" s="4">
+        <f>$B$50+$C$50*(2)</f>
+        <v/>
+      </c>
+      <c r="E21" s="3">
+        <f>D21/$B$9</f>
+        <v/>
+      </c>
+      <c r="F21" s="4">
+        <f>$B$50+$C$50*(2)</f>
+        <v/>
+      </c>
+      <c r="G21" s="3">
+        <f>F21/$B$9</f>
+        <v/>
+      </c>
+      <c r="H21" s="4">
+        <f>$B$50+$C$50*(1)</f>
+        <v/>
+      </c>
+      <c r="I21" s="3">
+        <f>H21/$B$9</f>
+        <v/>
+      </c>
+      <c r="J21" s="4">
+        <f>$B$50+$C$50*(1)</f>
+        <v/>
+      </c>
+      <c r="K21" s="3">
+        <f>J21/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>International freight</t>
+        </is>
+      </c>
+      <c r="B22" s="24">
+        <f>$B$51+$C$51*($B$6)</f>
+        <v/>
+      </c>
+      <c r="C22" s="25">
+        <f>B22/$B$9</f>
+        <v/>
+      </c>
+      <c r="D22" s="4">
+        <f>$B$51+$C$51*(2)</f>
+        <v/>
+      </c>
+      <c r="E22" s="3">
+        <f>D22/$B$9</f>
+        <v/>
+      </c>
+      <c r="F22" s="4">
+        <f>$B$51+$C$51*(2)</f>
+        <v/>
+      </c>
+      <c r="G22" s="3">
+        <f>F22/$B$9</f>
+        <v/>
+      </c>
+      <c r="H22" s="4">
+        <f>$B$51+$C$51*(1)</f>
+        <v/>
+      </c>
+      <c r="I22" s="3">
+        <f>H22/$B$9</f>
+        <v/>
+      </c>
+      <c r="J22" s="4">
+        <f>$B$51+$C$51*(1)</f>
+        <v/>
+      </c>
+      <c r="K22" s="3">
+        <f>J22/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>II - Import duty</t>
+        </is>
+      </c>
+      <c r="B23" s="24">
+        <f>($B$52+$C$52*($B$6))*(1-($B$5))</f>
+        <v/>
+      </c>
+      <c r="C23" s="25">
+        <f>B23/$B$9</f>
+        <v/>
+      </c>
+      <c r="D23" s="4">
+        <f>($B$52+$C$52*(2))*(1-(0))</f>
+        <v/>
+      </c>
+      <c r="E23" s="3">
+        <f>D23/$B$9</f>
+        <v/>
+      </c>
+      <c r="F23" s="4">
+        <f>($B$52+$C$52*(2))*(1-(1))</f>
+        <v/>
+      </c>
+      <c r="G23" s="3">
+        <f>F23/$B$9</f>
+        <v/>
+      </c>
+      <c r="H23" s="4">
+        <f>($B$52+$C$52*(1))*(1-(0))</f>
+        <v/>
+      </c>
+      <c r="I23" s="3">
+        <f>H23/$B$9</f>
+        <v/>
+      </c>
+      <c r="J23" s="4">
+        <f>($B$52+$C$52*(1))*(1-(1))</f>
+        <v/>
+      </c>
+      <c r="K23" s="3">
+        <f>J23/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Domestic freight</t>
+        </is>
+      </c>
+      <c r="B24" s="24">
+        <f>$B$53</f>
+        <v/>
+      </c>
+      <c r="C24" s="25">
+        <f>B24/$B$9</f>
+        <v/>
+      </c>
+      <c r="D24" s="4">
+        <f>$B$53</f>
+        <v/>
+      </c>
+      <c r="E24" s="3">
+        <f>D24/$B$9</f>
+        <v/>
+      </c>
+      <c r="F24" s="4">
+        <f>$B$53</f>
+        <v/>
+      </c>
+      <c r="G24" s="3">
+        <f>F24/$B$9</f>
+        <v/>
+      </c>
+      <c r="H24" s="4">
+        <f>$B$53</f>
+        <v/>
+      </c>
+      <c r="I24" s="3">
+        <f>H24/$B$9</f>
+        <v/>
+      </c>
+      <c r="J24" s="4">
+        <f>$B$53</f>
+        <v/>
+      </c>
+      <c r="K24" s="3">
+        <f>J24/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Supermetal - refurbishment / integration</t>
+        </is>
+      </c>
+      <c r="B25" s="24">
+        <f>$B$54</f>
+        <v/>
+      </c>
+      <c r="C25" s="25">
+        <f>B25/$B$9</f>
+        <v/>
+      </c>
+      <c r="D25" s="4">
+        <f>$B$54</f>
+        <v/>
+      </c>
+      <c r="E25" s="3">
+        <f>D25/$B$9</f>
+        <v/>
+      </c>
+      <c r="F25" s="4">
+        <f>$B$54</f>
+        <v/>
+      </c>
+      <c r="G25" s="3">
+        <f>F25/$B$9</f>
+        <v/>
+      </c>
+      <c r="H25" s="4">
+        <f>$B$54</f>
+        <v/>
+      </c>
+      <c r="I25" s="3">
+        <f>H25/$B$9</f>
+        <v/>
+      </c>
+      <c r="J25" s="4">
+        <f>$B$54</f>
+        <v/>
+      </c>
+      <c r="K25" s="3">
+        <f>J25/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>FINAL COST (with TP):</t>
+        </is>
+      </c>
+      <c r="B26" s="26">
+        <f>SUM(B19:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="16">
+        <f>B26/$B$9</f>
+        <v/>
+      </c>
+      <c r="D26" s="13">
+        <f>SUM(D19:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="14">
+        <f>D26/$B$9</f>
+        <v/>
+      </c>
+      <c r="F26" s="13">
+        <f>SUM(F19:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="14">
+        <f>F26/$B$9</f>
+        <v/>
+      </c>
+      <c r="H26" s="13">
+        <f>SUM(H19:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="14">
+        <f>H26/$B$9</f>
+        <v/>
+      </c>
+      <c r="J26" s="13">
+        <f>SUM(J19:J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="14">
+        <f>J26/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Base for margin (Final Cost - TP)</t>
+        </is>
+      </c>
+      <c r="B27" s="24">
+        <f>B26-B21</f>
+        <v/>
+      </c>
+      <c r="C27" s="25">
+        <f>B27/$B$9</f>
+        <v/>
+      </c>
+      <c r="D27" s="4">
+        <f>D26-D21</f>
+        <v/>
+      </c>
+      <c r="E27" s="3">
+        <f>D27/$B$9</f>
+        <v/>
+      </c>
+      <c r="F27" s="4">
+        <f>F26-F21</f>
+        <v/>
+      </c>
+      <c r="G27" s="3">
+        <f>F27/$B$9</f>
+        <v/>
+      </c>
+      <c r="H27" s="4">
+        <f>H26-H21</f>
+        <v/>
+      </c>
+      <c r="I27" s="3">
+        <f>H27/$B$9</f>
+        <v/>
+      </c>
+      <c r="J27" s="4">
+        <f>J26-J21</f>
+        <v/>
+      </c>
+      <c r="K27" s="3">
+        <f>J27/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Net price w/o TP (Base / (1 - TDM))</t>
+        </is>
+      </c>
+      <c r="B28" s="24">
+        <f>B27/(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="C28" s="25">
+        <f>B28/$B$9</f>
+        <v/>
+      </c>
+      <c r="D28" s="4">
+        <f>D27/(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="E28" s="3">
+        <f>D28/$B$9</f>
+        <v/>
+      </c>
+      <c r="F28" s="4">
+        <f>F27/(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="G28" s="3">
+        <f>F28/$B$9</f>
+        <v/>
+      </c>
+      <c r="H28" s="4">
+        <f>H27/(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="I28" s="3">
+        <f>H28/$B$9</f>
+        <v/>
+      </c>
+      <c r="J28" s="4">
+        <f>J27/(1-$B$10)</f>
+        <v/>
+      </c>
+      <c r="K28" s="3">
+        <f>J28/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>NET PRICE ('OUR PRICE'):</t>
+        </is>
+      </c>
+      <c r="B29" s="26">
+        <f>B28+B21</f>
+        <v/>
+      </c>
+      <c r="C29" s="16">
+        <f>B29/$B$9</f>
+        <v/>
+      </c>
+      <c r="D29" s="13">
+        <f>D28+D21</f>
+        <v/>
+      </c>
+      <c r="E29" s="14">
+        <f>D29/$B$9</f>
+        <v/>
+      </c>
+      <c r="F29" s="13">
+        <f>F28+F21</f>
+        <v/>
+      </c>
+      <c r="G29" s="14">
+        <f>F29/$B$9</f>
+        <v/>
+      </c>
+      <c r="H29" s="13">
+        <f>H28+H21</f>
+        <v/>
+      </c>
+      <c r="I29" s="14">
+        <f>H29/$B$9</f>
+        <v/>
+      </c>
+      <c r="J29" s="13">
+        <f>J28+J21</f>
+        <v/>
+      </c>
+      <c r="K29" s="14">
+        <f>J29/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>+ PIS/COFINS (gross-up)</t>
+        </is>
+      </c>
+      <c r="B30" s="24">
+        <f>B29/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="C30" s="25">
+        <f>B30/$B$9</f>
+        <v/>
+      </c>
+      <c r="D30" s="4">
+        <f>D29/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="E30" s="3">
+        <f>D30/$B$9</f>
+        <v/>
+      </c>
+      <c r="F30" s="4">
+        <f>F29/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="G30" s="3">
+        <f>F30/$B$9</f>
+        <v/>
+      </c>
+      <c r="H30" s="4">
+        <f>H29/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="I30" s="3">
+        <f>H30/$B$9</f>
+        <v/>
+      </c>
+      <c r="J30" s="4">
+        <f>J29/(1-$B$11)</f>
+        <v/>
+      </c>
+      <c r="K30" s="3">
+        <f>J30/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>+ ICMS (gross-up)</t>
+        </is>
+      </c>
+      <c r="B31" s="24">
+        <f>B30/(1-$B$12)</f>
+        <v/>
+      </c>
+      <c r="C31" s="25">
+        <f>B31/$B$9</f>
+        <v/>
+      </c>
+      <c r="D31" s="4">
+        <f>D30/(1-$B$12)</f>
+        <v/>
+      </c>
+      <c r="E31" s="3">
+        <f>D31/$B$9</f>
+        <v/>
+      </c>
+      <c r="F31" s="4">
+        <f>F30/(1-$B$12)</f>
+        <v/>
+      </c>
+      <c r="G31" s="3">
+        <f>F31/$B$9</f>
+        <v/>
+      </c>
+      <c r="H31" s="4">
+        <f>H30/(1-$B$12)</f>
+        <v/>
+      </c>
+      <c r="I31" s="3">
+        <f>H31/$B$9</f>
+        <v/>
+      </c>
+      <c r="J31" s="4">
+        <f>J30/(1-$B$12)</f>
+        <v/>
+      </c>
+      <c r="K31" s="3">
+        <f>J31/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>+ IPI (on top)</t>
+        </is>
+      </c>
+      <c r="B32" s="24">
+        <f>B31*$B$13</f>
+        <v/>
+      </c>
+      <c r="C32" s="25">
+        <f>B32/$B$9</f>
+        <v/>
+      </c>
+      <c r="D32" s="4">
+        <f>D31*$B$13</f>
+        <v/>
+      </c>
+      <c r="E32" s="3">
+        <f>D32/$B$9</f>
+        <v/>
+      </c>
+      <c r="F32" s="4">
+        <f>F31*$B$13</f>
+        <v/>
+      </c>
+      <c r="G32" s="3">
+        <f>F32/$B$9</f>
+        <v/>
+      </c>
+      <c r="H32" s="4">
+        <f>H31*$B$13</f>
+        <v/>
+      </c>
+      <c r="I32" s="3">
+        <f>H32/$B$9</f>
+        <v/>
+      </c>
+      <c r="J32" s="4">
+        <f>J31*$B$13</f>
+        <v/>
+      </c>
+      <c r="K32" s="3">
+        <f>J32/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>FINAL CLIENT PRICE:</t>
+        </is>
+      </c>
+      <c r="B33" s="26">
+        <f>B31+B32</f>
+        <v/>
+      </c>
+      <c r="C33" s="16">
+        <f>B33/$B$9</f>
+        <v/>
+      </c>
+      <c r="D33" s="13">
+        <f>D31+D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="14">
+        <f>D33/$B$9</f>
+        <v/>
+      </c>
+      <c r="F33" s="13">
+        <f>F31+F32</f>
+        <v/>
+      </c>
+      <c r="G33" s="14">
+        <f>F33/$B$9</f>
+        <v/>
+      </c>
+      <c r="H33" s="13">
+        <f>H31+H32</f>
+        <v/>
+      </c>
+      <c r="I33" s="14">
+        <f>H33/$B$9</f>
+        <v/>
+      </c>
+      <c r="J33" s="13">
+        <f>J31+J32</f>
+        <v/>
+      </c>
+      <c r="K33" s="14">
+        <f>J33/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>WHAT DRIVES THE FINAL CLIENT PRICE  (base case)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Removing ALL import duty (II) lowers the Final Client Price by</t>
+        </is>
+      </c>
+      <c r="B37" s="27">
+        <f>D33-F33</f>
+        <v/>
+      </c>
+      <c r="C37" s="3">
+        <f>B37/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Local output taxes (PIS/COFINS + ICMS + IPI) add on top of Net Price</t>
+        </is>
+      </c>
+      <c r="B38" s="27">
+        <f>D33-D29</f>
+        <v/>
+      </c>
+      <c r="C38" s="3">
+        <f>B38/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Local taxes are how many times bigger than the II effect?</t>
+        </is>
+      </c>
+      <c r="B39" s="28">
+        <f>B38/B37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Final Client Price with NO II and 1 battery set, vs. US reference</t>
+        </is>
+      </c>
+      <c r="B40" s="21">
+        <f>J33/$B$9</f>
+        <v/>
+      </c>
+      <c r="C40" s="17">
+        <f>B40/$B$14-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>- II (import duty) sits inside the cost, so it is multiplied by the margin (1/(1-TDM)) and then by the local tax cascade - removing it is worth about 2.7x its face value in the final price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>- Even so, the local output taxes (PIS/COFINS, ICMS, IPI) stack on the whole price and outweigh the II effect - that is the point of this tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>- Battery sets: II, TP and freight of the batteries scale with the quantity; the row values come from the Final Cost List (84A222059P5, group without historical TP -&gt; 17.2%, no confirmed NCM -&gt; II 18%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>BASE VALUES (read from the P&amp;L tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1">
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>Imported items, excluding batteries</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>Batteries - value per set (current BOM has 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Raw cost - imported items</t>
+        </is>
+      </c>
+      <c r="B48" s="4">
+        <f>'Executive Summary (P&amp;L)'!B10-2*C48</f>
+        <v/>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>79995.64</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Raw cost - PAC items</t>
+        </is>
+      </c>
+      <c r="B49" s="4">
+        <f>'Executive Summary (P&amp;L)'!B11</f>
+        <v/>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TP - Transfer Price</t>
+        </is>
+      </c>
+      <c r="B50" s="4">
+        <f>'Executive Summary (P&amp;L)'!B12-2*C50</f>
+        <v/>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>13759.25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>International freight</t>
+        </is>
+      </c>
+      <c r="B51" s="4">
+        <f>'Executive Summary (P&amp;L)'!B13-2*C51</f>
+        <v/>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>1152.78</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>II - Import duty</t>
+        </is>
+      </c>
+      <c r="B52" s="4">
+        <f>'Executive Summary (P&amp;L)'!B14-2*C52</f>
+        <v/>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>17083.38</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Domestic freight</t>
+        </is>
+      </c>
+      <c r="B53" s="4">
+        <f>'Executive Summary (P&amp;L)'!B15</f>
+        <v/>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Supermetal - refurbishment / integration</t>
+        </is>
+      </c>
+      <c r="B54" s="4">
+        <f>'Executive Summary (P&amp;L)'!B16</f>
+        <v/>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A44:H44"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"0,1"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Pathfinder_Cost_Summary_EN.xlsx
+++ b/Pathfinder_Cost_Summary_EN.xlsx
@@ -10771,7 +10771,7 @@
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>900000</v>
+        <v>899999.9999999999</v>
       </c>
     </row>
     <row r="62">
@@ -10785,7 +10785,7 @@
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>80500</v>
+        <v>80490</v>
       </c>
     </row>
     <row r="63">
@@ -10799,7 +10799,7 @@
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>16800</v>
+        <v>16842.85660194175</v>
       </c>
     </row>
     <row r="64">
@@ -10813,7 +10813,7 @@
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>715700</v>
+        <v>715697.9140243899</v>
       </c>
     </row>
     <row r="65">
@@ -10885,7 +10885,7 @@
     <row r="73" ht="60" customHeight="1" s="31">
       <c r="A73" s="51" t="inlineStr">
         <is>
-          <t>- Source: 'Planilha de Custos de Importacao - Pathfinder completo- Set 26.xlsx' (sheet 'Pathfinder Pronto') - this workbook is NOT in the repo, so these 5 values are transcribed from the footnote of MRS_Pathfinder_Simulation_Local_Taxes_Bilingual.pptx, not computed live. Different scope than the 4 scenarios above: this is a finished, already-built unit (no Wabtec Brasil margin, no TP, no Supermetal refurbishment - it's a straight import of a complete product), so it is not an apples-to-apples 5th column of the scenario table. Get the source workbook to make this row live.</t>
+          <t>- Source: read LIVE from 'Planilha de Custos de Importacao - Pathfinder completo- Set 26.xlsx', sheet 'Pathfinder Pronto' (cells H24, I22, I26, I27, I28, I35, I56). Different scope than the 4 scenarios above: this is a finished, already-built unit (no Wabtec Brasil margin, no TP, no Supermetal refurbishment - it's a straight import of a complete product), so it is not an apples-to-apples 5th column of the scenario table.</t>
         </is>
       </c>
     </row>
